--- a/बजेट माग estimate/नगर बजेट estimate/लाँकुरी बोट देवी सुमारा सडक/लाँकुरी बोट देवी सुमारा सडक.xlsx
+++ b/बजेट माग estimate/नगर बजेट estimate/लाँकुरी बोट देवी सुमारा सडक/लाँकुरी बोट देवी सुमारा सडक.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6823DE74-7B98-4A3C-BD18-16566A3EF7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="estimate" sheetId="12" r:id="rId1"/>
@@ -49,7 +50,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="0">estimate!$1:$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">gravel!$1:$8</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -237,10 +238,10 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="0.0"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="13" x14ac:knownFonts="1">
     <font>
@@ -388,9 +389,9 @@
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
@@ -402,107 +403,107 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="2" fontId="4" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -511,35 +512,35 @@
     <xf numFmtId="2" fontId="4" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma 2" xfId="3"/>
+    <cellStyle name="Comma 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="2"/>
-    <cellStyle name="Normal 3" xfId="5"/>
-    <cellStyle name="Percent 2" xfId="4"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="Normal 3" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
+    <cellStyle name="Percent 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
@@ -555,7 +556,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -649,7 +650,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -708,7 +709,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink3.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -772,7 +773,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink4.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Datasheet"/>
@@ -831,9 +832,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -871,9 +872,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -908,7 +909,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -943,7 +944,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1116,116 +1117,116 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K46"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="3"/>
+    <col min="1" max="1" width="4.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="3"/>
     <col min="8" max="8" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="3"/>
+    <col min="9" max="9" width="9.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="51" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>28</v>
       </c>
@@ -1242,7 +1243,7 @@
       <c r="J7" s="43"/>
       <c r="K7" s="43"/>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -1277,7 +1278,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="21" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" s="21" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>1</v>
       </c>
@@ -1294,7 +1295,7 @@
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="16" t="s">
         <v>39</v>
@@ -1321,7 +1322,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="16" t="s">
         <v>26</v>
@@ -1346,7 +1347,7 @@
       </c>
       <c r="K11" s="18"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="22" t="s">
         <v>46</v>
@@ -1364,7 +1365,7 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="22"/>
       <c r="C13" s="12"/>
@@ -1377,7 +1378,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>2</v>
       </c>
@@ -1394,7 +1395,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="16" t="str">
         <f>B10</f>
@@ -1423,7 +1424,7 @@
       <c r="J15" s="13"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
         <v>26</v>
@@ -1448,7 +1449,7 @@
       </c>
       <c r="K16" s="18"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="22" t="s">
         <v>32</v>
@@ -1466,7 +1467,7 @@
       </c>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="11"/>
       <c r="C18" s="12"/>
@@ -1479,7 +1480,7 @@
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="74.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>3</v>
       </c>
@@ -1496,7 +1497,7 @@
       <c r="J19" s="13"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="10"/>
       <c r="B20" s="16" t="str">
         <f>B15</f>
@@ -1525,7 +1526,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15"/>
       <c r="B21" s="16" t="s">
         <v>26</v>
@@ -1550,7 +1551,7 @@
       </c>
       <c r="K21" s="18"/>
     </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="10"/>
       <c r="B22" s="22" t="s">
         <v>30</v>
@@ -1568,7 +1569,7 @@
       </c>
       <c r="K22" s="12"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="22" t="s">
         <v>29</v>
@@ -1586,7 +1587,7 @@
       </c>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="22" t="s">
         <v>31</v>
@@ -1604,7 +1605,7 @@
       </c>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="22" t="s">
         <v>34</v>
@@ -1622,7 +1623,7 @@
       </c>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="22" t="s">
         <v>35</v>
@@ -1640,7 +1641,7 @@
       </c>
       <c r="K26" s="12"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="22"/>
       <c r="C27" s="12"/>
@@ -1653,7 +1654,7 @@
       <c r="J27" s="13"/>
       <c r="K27" s="12"/>
     </row>
-    <row r="28" spans="1:11" s="21" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" s="21" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>4</v>
       </c>
@@ -1678,7 +1679,7 @@
       <c r="J28" s="20"/>
       <c r="K28" s="32"/>
     </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" s="10"/>
       <c r="B29" s="16" t="str">
         <f>B10</f>
@@ -1709,7 +1710,7 @@
       <c r="J29" s="13"/>
       <c r="K29" s="12"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="16"/>
       <c r="C30" s="12">
@@ -1737,7 +1738,7 @@
       <c r="J30" s="13"/>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15"/>
       <c r="B31" s="16" t="s">
         <v>26</v>
@@ -1762,7 +1763,7 @@
       </c>
       <c r="K31" s="18"/>
     </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="10"/>
       <c r="B32" s="22" t="s">
         <v>44</v>
@@ -1780,7 +1781,7 @@
       </c>
       <c r="K32" s="12"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="22" t="s">
         <v>45</v>
@@ -1798,7 +1799,7 @@
       </c>
       <c r="K33" s="12"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="22"/>
       <c r="C34" s="12"/>
@@ -1811,7 +1812,7 @@
       <c r="J34" s="13"/>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
         <v>5</v>
       </c>
@@ -1840,7 +1841,7 @@
       </c>
       <c r="K35" s="18"/>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="15"/>
       <c r="B36" s="25"/>
       <c r="C36" s="17"/>
@@ -1853,7 +1854,7 @@
       <c r="J36" s="13"/>
       <c r="K36" s="18"/>
     </row>
-    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
         <v>6</v>
       </c>
@@ -1882,7 +1883,7 @@
       </c>
       <c r="K37" s="18"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" s="15"/>
       <c r="B38" s="25"/>
       <c r="C38" s="17"/>
@@ -1895,7 +1896,7 @@
       <c r="J38" s="13"/>
       <c r="K38" s="18"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="26"/>
       <c r="B39" s="27" t="s">
         <v>19</v>
@@ -1913,7 +1914,7 @@
       </c>
       <c r="K39" s="30"/>
     </row>
-    <row r="41" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="31"/>
       <c r="B41" s="32" t="s">
         <v>18</v>
@@ -1933,7 +1934,7 @@
       <c r="J41" s="36"/>
       <c r="K41" s="37"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B42" s="32" t="s">
         <v>20</v>
       </c>
@@ -1943,7 +1944,7 @@
       <c r="D42" s="45"/>
       <c r="E42" s="33"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" s="32" t="s">
         <v>21</v>
       </c>
@@ -1957,7 +1958,7 @@
         <v>83.972542173502262</v>
       </c>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" s="32" t="s">
         <v>25</v>
       </c>
@@ -1971,7 +1972,7 @@
         <v>16.027457826497738</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" s="32" t="s">
         <v>22</v>
       </c>
@@ -1984,7 +1985,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" s="32" t="s">
         <v>23</v>
       </c>
@@ -1999,13 +2000,6 @@
     </row>
   </sheetData>
   <mergeCells count="15">
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C45:D45"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="A7:F7"/>
@@ -2014,126 +2008,136 @@
     <mergeCell ref="C42:D42"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;LPrepared By:&amp;CChecked By:&amp;RApproved By:</oddFooter>
   </headerFooter>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="36" max="10" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K47"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="30.88671875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="4.44140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.44140625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="8.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="7.33203125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="9.109375" style="3"/>
+    <col min="1" max="1" width="4.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="30.85546875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="4.42578125" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.42578125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="8.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="7.28515625" style="3" customWidth="1"/>
+    <col min="7" max="7" width="9.140625" style="3"/>
     <col min="8" max="8" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="3"/>
+    <col min="9" max="9" width="9.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49"/>
-      <c r="C1" s="49"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-    </row>
-    <row r="2" spans="1:11" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="A2" s="50" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+    </row>
+    <row r="2" spans="1:11" ht="22.5" x14ac:dyDescent="0.25">
+      <c r="A2" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="50"/>
-      <c r="C2" s="50"/>
-      <c r="D2" s="50"/>
-      <c r="E2" s="50"/>
-      <c r="F2" s="50"/>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-      <c r="J2" s="50"/>
-      <c r="K2" s="50"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="51" t="s">
+      <c r="B2" s="48"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="49" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="51"/>
-      <c r="F3" s="51"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="51"/>
-      <c r="I3" s="51"/>
-      <c r="J3" s="51"/>
-      <c r="K3" s="51"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A4" s="51" t="s">
+      <c r="B3" s="49"/>
+      <c r="C3" s="49"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
+      <c r="I3" s="49"/>
+      <c r="J3" s="49"/>
+      <c r="K3" s="49"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="51"/>
-      <c r="F4" s="51"/>
-      <c r="G4" s="51"/>
-      <c r="H4" s="51"/>
-      <c r="I4" s="51"/>
-      <c r="J4" s="51"/>
-      <c r="K4" s="51"/>
-    </row>
-    <row r="5" spans="1:11" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="A5" s="52" t="s">
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="49"/>
+      <c r="K4" s="49"/>
+    </row>
+    <row r="5" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A5" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="52"/>
-      <c r="K5" s="52"/>
-    </row>
-    <row r="6" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="47" t="s">
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="50"/>
+      <c r="F5" s="50"/>
+      <c r="G5" s="50"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+      <c r="J5" s="50"/>
+      <c r="K5" s="50"/>
+    </row>
+    <row r="6" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="51" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="47"/>
-      <c r="F6" s="47"/>
+      <c r="B6" s="51"/>
+      <c r="C6" s="51"/>
+      <c r="D6" s="51"/>
+      <c r="E6" s="51"/>
+      <c r="F6" s="51"/>
       <c r="G6" s="4"/>
-      <c r="H6" s="48" t="s">
+      <c r="H6" s="52" t="s">
         <v>24</v>
       </c>
-      <c r="I6" s="48"/>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48"/>
-    </row>
-    <row r="7" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="I6" s="52"/>
+      <c r="J6" s="52"/>
+      <c r="K6" s="52"/>
+    </row>
+    <row r="7" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" s="42" t="s">
         <v>28</v>
       </c>
@@ -2150,7 +2154,7 @@
       <c r="J7" s="43"/>
       <c r="K7" s="43"/>
     </row>
-    <row r="8" spans="1:11" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
         <v>5</v>
       </c>
@@ -2185,7 +2189,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:11" s="21" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" s="21" customFormat="1" ht="150" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>1</v>
       </c>
@@ -2202,7 +2206,7 @@
       <c r="J9" s="32"/>
       <c r="K9" s="32"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="10"/>
       <c r="B10" s="16" t="s">
         <v>39</v>
@@ -2229,7 +2233,7 @@
       <c r="J10" s="13"/>
       <c r="K10" s="12"/>
     </row>
-    <row r="11" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="15"/>
       <c r="B11" s="16" t="s">
         <v>26</v>
@@ -2254,7 +2258,7 @@
       </c>
       <c r="K11" s="18"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="10"/>
       <c r="B12" s="22" t="s">
         <v>46</v>
@@ -2272,7 +2276,7 @@
       </c>
       <c r="K12" s="12"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="10"/>
       <c r="B13" s="22"/>
       <c r="C13" s="12"/>
@@ -2285,7 +2289,7 @@
       <c r="J13" s="13"/>
       <c r="K13" s="12"/>
     </row>
-    <row r="14" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="105" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>2</v>
       </c>
@@ -2302,7 +2306,7 @@
       <c r="J14" s="12"/>
       <c r="K14" s="12"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="10"/>
       <c r="B15" s="16" t="str">
         <f>B10</f>
@@ -2331,7 +2335,7 @@
       <c r="J15" s="13"/>
       <c r="K15" s="12"/>
     </row>
-    <row r="16" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15"/>
       <c r="B16" s="16" t="s">
         <v>26</v>
@@ -2356,7 +2360,7 @@
       </c>
       <c r="K16" s="18"/>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="10"/>
       <c r="B17" s="22" t="s">
         <v>32</v>
@@ -2374,7 +2378,7 @@
       </c>
       <c r="K17" s="12"/>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="10"/>
       <c r="B18" s="22" t="s">
         <v>34</v>
@@ -2392,7 +2396,7 @@
       </c>
       <c r="K18" s="12"/>
     </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="10"/>
       <c r="B19" s="11"/>
       <c r="C19" s="12"/>
@@ -2405,7 +2409,7 @@
       <c r="J19" s="12"/>
       <c r="K19" s="12"/>
     </row>
-    <row r="20" spans="1:11" ht="72" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="75.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>3</v>
       </c>
@@ -2422,7 +2426,7 @@
       <c r="J20" s="13"/>
       <c r="K20" s="12"/>
     </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="10"/>
       <c r="B21" s="16" t="str">
         <f>B15</f>
@@ -2451,7 +2455,7 @@
       <c r="J21" s="13"/>
       <c r="K21" s="12"/>
     </row>
-    <row r="22" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="15"/>
       <c r="B22" s="16" t="s">
         <v>26</v>
@@ -2476,7 +2480,7 @@
       </c>
       <c r="K22" s="18"/>
     </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="10"/>
       <c r="B23" s="22" t="s">
         <v>30</v>
@@ -2494,7 +2498,7 @@
       </c>
       <c r="K23" s="12"/>
     </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" s="10"/>
       <c r="B24" s="22" t="s">
         <v>29</v>
@@ -2512,7 +2516,7 @@
       </c>
       <c r="K24" s="12"/>
     </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" s="10"/>
       <c r="B25" s="22" t="s">
         <v>31</v>
@@ -2530,7 +2534,7 @@
       </c>
       <c r="K25" s="12"/>
     </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="10"/>
       <c r="B26" s="22" t="s">
         <v>34</v>
@@ -2548,7 +2552,7 @@
       </c>
       <c r="K26" s="12"/>
     </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" s="10"/>
       <c r="B27" s="22" t="s">
         <v>35</v>
@@ -2566,7 +2570,7 @@
       </c>
       <c r="K27" s="12"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="10"/>
       <c r="B28" s="22"/>
       <c r="C28" s="12"/>
@@ -2579,7 +2583,7 @@
       <c r="J28" s="13"/>
       <c r="K28" s="12"/>
     </row>
-    <row r="29" spans="1:11" s="21" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" s="21" customFormat="1" ht="90" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>4</v>
       </c>
@@ -2604,7 +2608,7 @@
       <c r="J29" s="20"/>
       <c r="K29" s="32"/>
     </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" s="10"/>
       <c r="B30" s="16" t="str">
         <f>B10</f>
@@ -2635,7 +2639,7 @@
       <c r="J30" s="13"/>
       <c r="K30" s="12"/>
     </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="10"/>
       <c r="B31" s="16"/>
       <c r="C31" s="12">
@@ -2663,7 +2667,7 @@
       <c r="J31" s="13"/>
       <c r="K31" s="12"/>
     </row>
-    <row r="32" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="15"/>
       <c r="B32" s="16" t="s">
         <v>26</v>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="K32" s="18"/>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="10"/>
       <c r="B33" s="22" t="s">
         <v>44</v>
@@ -2706,7 +2710,7 @@
       </c>
       <c r="K33" s="12"/>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="10"/>
       <c r="B34" s="22" t="s">
         <v>45</v>
@@ -2724,7 +2728,7 @@
       </c>
       <c r="K34" s="12"/>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="10"/>
       <c r="B35" s="22"/>
       <c r="C35" s="12"/>
@@ -2737,7 +2741,7 @@
       <c r="J35" s="13"/>
       <c r="K35" s="12"/>
     </row>
-    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="15">
         <v>5</v>
       </c>
@@ -2766,7 +2770,7 @@
       </c>
       <c r="K36" s="18"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="15"/>
       <c r="B37" s="25"/>
       <c r="C37" s="17"/>
@@ -2779,7 +2783,7 @@
       <c r="J37" s="13"/>
       <c r="K37" s="18"/>
     </row>
-    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="15">
         <v>6</v>
       </c>
@@ -2808,7 +2812,7 @@
       </c>
       <c r="K38" s="18"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" s="15"/>
       <c r="B39" s="25"/>
       <c r="C39" s="17"/>
@@ -2821,7 +2825,7 @@
       <c r="J39" s="13"/>
       <c r="K39" s="18"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" s="26"/>
       <c r="B40" s="27" t="s">
         <v>19</v>
@@ -2839,7 +2843,7 @@
       </c>
       <c r="K40" s="30"/>
     </row>
-    <row r="42" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" s="21" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="31"/>
       <c r="B42" s="32" t="s">
         <v>18</v>
@@ -2859,7 +2863,7 @@
       <c r="J42" s="36"/>
       <c r="K42" s="37"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B43" s="32" t="s">
         <v>20</v>
       </c>
@@ -2869,7 +2873,7 @@
       <c r="D43" s="45"/>
       <c r="E43" s="33"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B44" s="32" t="s">
         <v>21</v>
       </c>
@@ -2883,7 +2887,7 @@
         <v>84.166272401936837</v>
       </c>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B45" s="32" t="s">
         <v>25</v>
       </c>
@@ -2897,7 +2901,7 @@
         <v>15.833727598063163</v>
       </c>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B46" s="32" t="s">
         <v>22</v>
       </c>
@@ -2910,7 +2914,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="B47" s="32" t="s">
         <v>23</v>
       </c>
@@ -2925,6 +2929,13 @@
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A5:K5"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C47:D47"/>
     <mergeCell ref="A7:F7"/>
@@ -2933,13 +2944,6 @@
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="C45:D45"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="H6:K6"/>
   </mergeCells>
   <pageMargins left="0.70866141732283505" right="0.70866141732283505" top="0.74803149606299202" bottom="0.74803149606299202" header="0.31496062992126" footer="0.31496062992126"/>
   <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="1200" r:id="rId1"/>
